--- a/学生导入模板.xlsx
+++ b/学生导入模板.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="学生名单" sheetId="1" r:id="R88b564f223de43bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="学生名单" sheetId="1" r:id="R15318117120846d4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -44,12 +44,37 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF173B68"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2E75B6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7FAFD"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0E7A6D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF8F6"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -111,7 +136,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="24">
+  <x:cellXfs count="46">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -154,6 +179,48 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -358,85 +425,126 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="27" t="str">
         <x:v>学生名单 Excel 导入模板</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="D1" s="19" t="str">
+      <x:c r="B1" s="27"/>
+      <x:c r="C1" s="27"/>
+      <x:c r="D1" s="27"/>
+      <x:c r="E1"/>
+      <x:c r="F1" s="41" t="str">
         <x:v>填写说明</x:v>
       </x:c>
-      <x:c r="E1" s="19"/>
-      <x:c r="F1" s="19"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="D2" s="23" t="str">
-        <x:v>1. 必须保留“学号”和“姓名”表头。</x:v>
-      </x:c>
-      <x:c r="E2" s="23"/>
-      <x:c r="F2" s="23"/>
-    </x:row>
-    <x:row r="3" ht="25" customHeight="1">
-      <x:c r="A3" s="9" t="str">
+      <x:c r="G1" s="41"/>
+      <x:c r="H1" s="41"/>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2" s="45" t="str">
+        <x:v>1. 名单只能通过 Excel 修改，必须保留四列表头。</x:v>
+      </x:c>
+      <x:c r="G2" s="45"/>
+      <x:c r="H2" s="45"/>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="32" t="str">
         <x:v>学号</x:v>
       </x:c>
-      <x:c r="B3" s="9" t="str">
+      <x:c r="B3" s="32" t="str">
         <x:v>姓名</x:v>
       </x:c>
-      <x:c r="D3" s="23" t="str">
-        <x:v>2. 学号必须唯一，建议把学号列设置为文本。</x:v>
-      </x:c>
-      <x:c r="E3" s="23"/>
-      <x:c r="F3" s="23"/>
-    </x:row>
-    <x:row r="4" ht="25" customHeight="1">
-      <x:c r="A4" s="14" t="str">
+      <x:c r="C3" s="32" t="str">
+        <x:v>班级</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="str">
+        <x:v>参与点名</x:v>
+      </x:c>
+      <x:c r="E3"/>
+      <x:c r="F3" s="45" t="str">
+        <x:v>2. 学号必须唯一，并建议将学号列设置为文本。</x:v>
+      </x:c>
+      <x:c r="G3" s="45"/>
+      <x:c r="H3" s="45"/>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="37" t="str">
         <x:v>S001</x:v>
       </x:c>
-      <x:c r="B4" s="13" t="str">
+      <x:c r="B4" s="36" t="str">
         <x:v>张三</x:v>
       </x:c>
-      <x:c r="D4" s="23" t="str">
-        <x:v>3. 可删除示例行后填写真实学生。</x:v>
-      </x:c>
-      <x:c r="E4" s="23"/>
-      <x:c r="F4" s="23"/>
-    </x:row>
-    <x:row r="5" ht="25" customHeight="1">
-      <x:c r="A5" s="14" t="str">
+      <x:c r="C4" s="36" t="str">
+        <x:v>高一（1）班</x:v>
+      </x:c>
+      <x:c r="D4" s="36" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4" s="45" t="str">
+        <x:v>3. 同一班级名称必须完全一致，程序会按班级分组。</x:v>
+      </x:c>
+      <x:c r="G4" s="45"/>
+      <x:c r="H4" s="45"/>
+    </x:row>
+    <x:row r="5" ht="28" customHeight="1">
+      <x:c r="A5" s="37" t="str">
         <x:v>S002</x:v>
       </x:c>
-      <x:c r="B5" s="13" t="str">
+      <x:c r="B5" s="36" t="str">
         <x:v>李四</x:v>
       </x:c>
-      <x:c r="D5" s="23" t="str">
-        <x:v>4. 支持 .xlsx 和 .xlsm 文件。</x:v>
-      </x:c>
-      <x:c r="E5" s="23"/>
-      <x:c r="F5" s="23"/>
-    </x:row>
-    <x:row r="6" ht="25" customHeight="1">
-      <x:c r="A6" s="14" t="str">
+      <x:c r="C5" s="36" t="str">
+        <x:v>高一（1）班</x:v>
+      </x:c>
+      <x:c r="D5" s="36" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5" s="45" t="str">
+        <x:v>4. “参与点名”填写“是”或“否”，请假可填“否”。</x:v>
+      </x:c>
+      <x:c r="G5" s="45"/>
+      <x:c r="H5" s="45"/>
+    </x:row>
+    <x:row r="6" ht="28" customHeight="1">
+      <x:c r="A6" s="37" t="str">
         <x:v>S003</x:v>
       </x:c>
-      <x:c r="B6" s="13" t="str">
+      <x:c r="B6" s="36" t="str">
         <x:v>王五</x:v>
       </x:c>
-      <x:c r="D6" s="23" t="str">
-        <x:v>5. 导入时，空白行会被自动忽略。</x:v>
-      </x:c>
-      <x:c r="E6" s="23"/>
-      <x:c r="F6" s="23"/>
-    </x:row>
-    <x:row r="7">
+      <x:c r="C6" s="36" t="str">
+        <x:v>高一（1）班</x:v>
+      </x:c>
+      <x:c r="D6" s="36" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6" s="45" t="str">
+        <x:v>5. 导入会整体替换当前名单，旧名单会自动备份。</x:v>
+      </x:c>
+      <x:c r="G6" s="45"/>
+      <x:c r="H6" s="45"/>
+    </x:row>
+    <x:row r="7" ht="28" customHeight="1">
       <x:c r="A7" s="15"/>
+      <x:c r="F7" s="45" t="str">
+        <x:v>6. 删除示例行后填写真实学生，再导入程序。</x:v>
+      </x:c>
+      <x:c r="G7" s="45"/>
+      <x:c r="H7" s="45"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="15"/>
@@ -1019,14 +1127,20 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:B1"/>
-    <x:mergeCell ref="D1:F1"/>
-    <x:mergeCell ref="D2:F2"/>
-    <x:mergeCell ref="D3:F3"/>
-    <x:mergeCell ref="D4:F4"/>
-    <x:mergeCell ref="D5:F5"/>
-    <x:mergeCell ref="D6:F6"/>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="F1:H1"/>
+    <x:mergeCell ref="F2:H2"/>
+    <x:mergeCell ref="F3:H3"/>
+    <x:mergeCell ref="F4:H4"/>
+    <x:mergeCell ref="F5:H5"/>
+    <x:mergeCell ref="F6:H6"/>
+    <x:mergeCell ref="F7:H7"/>
   </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="D4:D200">
+      <x:formula1>"是,否"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>